--- a/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I68" s="2"/>
@@ -4337,7 +4337,7 @@
       <c r="M4" s="9"/>
       <c r="N4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="9"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -4616,7 +4616,7 @@
       <c r="K8" s="10"/>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4741,7 +4741,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="9"/>

--- a/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4176,106 +4217,106 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">쑥대머리</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">겨를</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
 潢</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">보고</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="P3" s="18" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">쑥</t>
         </is>
@@ -4283,70 +4324,70 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지고</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
@@ -4354,78 +4395,78 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="26"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서름</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">보고</t>
         </is>
       </c>
-      <c r="L5" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M5" s="13" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
-      <c r="N5" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O5" s="13" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">머리</t>
         </is>
@@ -4433,289 +4474,289 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">없</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">봉양</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">지고</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나는</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q6" s="8"/>
+      <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">방</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K8" s="26"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q8" s="10"/>
+      <c r="Q8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">글</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋姑</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">못봤</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">한양</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">찬</t>
         </is>
       </c>
-      <c r="P9" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q9" s="11" t="inlineStr">
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
@@ -4723,74 +4764,74 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="25"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="G10" s="25"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">뻘</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">낭군</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">뿐</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
@@ -4798,79 +4839,79 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="26"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">형</t>
         </is>
@@ -4878,82 +4919,82 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">보고</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">용</t>
         </is>
@@ -4961,110 +5002,110 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K14" s="26"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="26"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
@@ -4194,28 +4194,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4322,17 +4322,17 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M4" s="25"/>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4569,13 +4569,13 @@
       <c r="G7" s="25"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="25"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K7" s="25"/>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5000,11 +5000,11 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="25"/>
@@ -5020,13 +5020,13 @@
       </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5039,24 +5039,24 @@
       <c r="K13" s="25"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="25"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O13" s="25"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
       <c r="E14" s="26"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5087,21 +5087,21 @@
       <c r="K14" s="26"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="M14" s="26"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="O14" s="26"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
@@ -4247,7 +4247,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">겨를</t>
+          <t xml:space="preserve">겨
+를</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -4288,7 +4289,8 @@
       </c>
       <c r="K3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">보고</t>
+          <t xml:space="preserve">보
+고</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
@@ -4367,7 +4369,8 @@
       </c>
       <c r="K4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">지고</t>
+          <t xml:space="preserve">지
+고</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
@@ -4418,7 +4421,8 @@
       </c>
       <c r="G5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">서름</t>
+          <t xml:space="preserve">서
+름</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -4438,7 +4442,8 @@
       </c>
       <c r="K5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">보고</t>
+          <t xml:space="preserve">보
+고</t>
         </is>
       </c>
       <c r="L5" s="23" t="inlineStr">
@@ -4468,7 +4473,8 @@
       </c>
       <c r="Q5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">머리</t>
+          <t xml:space="preserve">머
+리</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4497,8 @@
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉양</t>
+          <t xml:space="preserve">봉
+양</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -4513,7 +4520,8 @@
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">지고</t>
+          <t xml:space="preserve">지
+고</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -4523,7 +4531,8 @@
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">나는</t>
+          <t xml:space="preserve">나
+는</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -4712,7 +4721,8 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">못봤</t>
+          <t xml:space="preserve">못
+봤</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -4728,7 +4738,8 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">한양</t>
+          <t xml:space="preserve">한
+양</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -4803,7 +4814,8 @@
       </c>
       <c r="K10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">낭군</t>
+          <t xml:space="preserve">낭
+군</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -4966,7 +4978,8 @@
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">보고</t>
+          <t xml:space="preserve">보
+고</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">

--- a/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4245,7 +4268,7 @@
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">겨
 를</t>
@@ -4257,7 +4280,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -4267,7 +4290,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -4277,7 +4300,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4287,7 +4310,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">보
 고</t>
@@ -4298,7 +4321,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
@@ -4308,7 +4331,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
@@ -4318,7 +4341,7 @@
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">쑥</t>
         </is>
@@ -4331,13 +4354,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -4347,7 +4370,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
@@ -4357,7 +4380,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4367,7 +4390,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">지
 고</t>
@@ -4378,19 +4401,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="25"/>
+      <c r="O4" s="31"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
@@ -4403,7 +4426,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4413,13 +4436,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="32"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">서
 름</t>
@@ -4430,7 +4453,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
@@ -4440,7 +4463,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">보
 고</t>
@@ -4451,7 +4474,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
@@ -4461,7 +4484,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
@@ -4471,7 +4494,7 @@
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="Q5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">머
 리</t>
@@ -4485,7 +4508,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">없</t>
         </is>
@@ -4495,7 +4518,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">봉
 양</t>
@@ -4506,19 +4529,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="29"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">지
 고</t>
@@ -4529,7 +4552,7 @@
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 는</t>
@@ -4540,7 +4563,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
@@ -4550,7 +4573,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q6" s="22"/>
+      <c r="Q6" s="29"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -4559,7 +4582,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4569,31 +4592,31 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="31"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
@@ -4603,7 +4626,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">방</t>
         </is>
@@ -4613,7 +4636,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q7" s="25"/>
+      <c r="Q7" s="31"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -4622,7 +4645,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -4632,7 +4655,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -4643,7 +4666,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4653,7 +4676,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -4663,14 +4686,14 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="26"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -4680,7 +4703,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O8" s="26" t="inlineStr">
+      <c r="O8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4690,7 +4713,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q8" s="26"/>
+      <c r="Q8" s="32"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -4699,7 +4722,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4709,7 +4732,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">글</t>
         </is>
@@ -4719,7 +4742,7 @@
           <t xml:space="preserve">淋姑</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 봤</t>
@@ -4730,13 +4753,13 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="29"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">한
 양</t>
@@ -4747,7 +4770,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -4757,7 +4780,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">찬</t>
         </is>
@@ -4767,7 +4790,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="inlineStr">
+      <c r="Q9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
@@ -4780,7 +4803,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
@@ -4790,19 +4813,19 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E10" s="25"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I10" s="28" t="inlineStr">
+      <c r="I10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">뻘</t>
         </is>
@@ -4812,7 +4835,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">낭
 군</t>
@@ -4823,7 +4846,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">뿐</t>
         </is>
@@ -4833,7 +4856,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -4843,7 +4866,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
@@ -4856,7 +4879,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4867,13 +4890,13 @@
 △</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -4883,7 +4906,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
@@ -4893,7 +4916,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -4903,7 +4926,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4913,7 +4936,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O11" s="26" t="inlineStr">
+      <c r="O11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4923,7 +4946,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q11" s="26" t="inlineStr">
+      <c r="Q11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">형</t>
         </is>
@@ -4936,7 +4959,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4946,7 +4969,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
@@ -4956,7 +4979,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4966,7 +4989,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -4976,7 +4999,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">보
 고</t>
@@ -4987,7 +5010,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -4997,7 +5020,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5007,7 +5030,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">용</t>
         </is>
@@ -5020,13 +5043,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -5036,38 +5059,38 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O13" s="25"/>
+      <c r="O13" s="31"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -5076,49 +5099,49 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="26"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K14" s="26"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M14" s="26"/>
+      <c r="M14" s="32"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O14" s="26"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q14" s="26"/>
+      <c r="Q14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -238,27 +233,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -353,7 +327,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">95</t>
+          <t xml:space="preserve">96</t>
         </is>
       </c>
     </row>
@@ -365,7 +339,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
@@ -425,7 +399,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12정간, 굵은 선 3칸마다. 오른쪽 여백 "1. (쑥대머리) 단가, 중모리", "키 신형(?)" 표기. 8줄 모두 사용. 청성(氵)이 많아 潢·淋·汰 다수. 하단 메모칸에 교정 지시 "※ 潢 ⇒ 潢(氵無/無)". 가사: 각 율명 줄 오른쪽 가사 칸을 전사함(쑥대머리 귀신형용 / 적막옥방에 찬자리에 / 생각나는것은 님뿐이라 / 보고지고 보고지고 한양낭군을 보고 / 오리정 정별후로 / 일장서름 가 못봤으니 / 부모봉양 글공부 / 겨를이 없어 이허는가). 검수: 3·4줄, 5·6줄이 서로 바뀌어 있던 것을 번호대로(오른쪽=1) 바로잡음.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~8 줄, 1~12 정간), 12정간·굵은 선 3칸마다 → 3/4·12, 8줄 모두 사용, 한 곡. 오른쪽 여백 '1. (쑥대머리) 단가, 중모리'. 이전 판독의 淋·淋潢 은 대부분 氵姑(㴌). 潢 오른쪽 아래 겹 곡선 ')' 꾸밈은 潢^ 로 적음 — 하단 메모칸 '※ 潢) ⇒ 潢 아래 無(곡선)' 즉 潢에서 無로 꺾어 내리는 표시. 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
@@ -611,26 +585,22 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋潢</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋潢</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">쑥</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청황계 두 글자 겹침</t>
-        </is>
-      </c>
+      <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -656,12 +626,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -695,12 +665,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -837,26 +808,22 @@
       <c r="F8" s="2">
         <v>3</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">귀신형용의 '귀'(키처럼 보임)</t>
-        </is>
-      </c>
+      <c r="J8" s="4"/>
       <c r="K8" s="2"/>
     </row>
     <row r="9">
@@ -999,12 +966,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -1034,12 +1001,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1144,12 +1111,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1159,7 +1126,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氵계열, 淋/潢? 확실치 않음</t>
+          <t xml:space="preserve">가사 '각'처럼 보임(적막)</t>
         </is>
       </c>
       <c r="K16" s="2"/>
@@ -1187,12 +1154,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1226,12 +1193,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1263,22 +1230,26 @@
       <c r="F19" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J19" s="4"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">氵 희미, 南?</t>
+        </is>
+      </c>
       <c r="K19" s="2"/>
     </row>
     <row r="20">
@@ -1304,12 +1275,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1570,12 +1541,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I27" s="2"/>
@@ -1603,26 +1574,22 @@
       <c r="F28" s="2">
         <v>1</v>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵계열</t>
-        </is>
-      </c>
+      <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
     <row r="29">
@@ -1648,12 +1615,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1766,12 +1734,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1993,12 +1961,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢
+潢</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2032,12 +2001,13 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢
+潢</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2071,12 +2041,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢
+潢</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2110,12 +2081,13 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢
+潢</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2184,12 +2156,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I43" s="2"/>
@@ -2219,12 +2191,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢
+㴌</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2258,12 +2231,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">㴌|㴌</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">㴌
+㴌</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2297,12 +2271,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2336,12 +2310,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢
+潢</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2383,7 +2358,11 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I48" s="2"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
@@ -2410,15 +2389,19 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I49" s="2"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
@@ -2443,26 +2426,22 @@
       <c r="F50" s="2">
         <v>1</v>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵계열</t>
-        </is>
-      </c>
+      <c r="J50" s="4"/>
       <c r="K50" s="2"/>
     </row>
     <row r="51">
@@ -2488,12 +2467,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2527,12 +2506,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2634,26 +2613,18 @@
       <c r="F55" s="2">
         <v>2</v>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정별후로의 '전'(정?)</t>
-        </is>
-      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="4"/>
       <c r="K55" s="2"/>
     </row>
     <row r="56">
@@ -2679,15 +2650,19 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I56" s="2"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전</t>
+        </is>
+      </c>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
@@ -2712,26 +2687,22 @@
       <c r="F57" s="2">
         <v>3</v>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뻘</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정별후로의 '별'</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">별</t>
+        </is>
+      </c>
+      <c r="J57" s="4"/>
       <c r="K57" s="2"/>
     </row>
     <row r="58">
@@ -2757,12 +2728,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2796,12 +2767,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2835,13 +2806,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I60" s="2"/>
@@ -2858,32 +2828,29 @@
         </is>
       </c>
       <c r="C61" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E61" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F61" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I61" s="2"/>
       <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
@@ -2903,24 +2870,24 @@
         <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">장</t>
+          <t xml:space="preserve">일</t>
         </is>
       </c>
       <c r="J62" s="4"/>
@@ -2942,24 +2909,24 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" s="2">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서름</t>
+          <t xml:space="preserve">장</t>
         </is>
       </c>
       <c r="J63" s="4"/>
@@ -2981,22 +2948,27 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">㴌|潢^</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I64" s="2"/>
+          <t xml:space="preserve">㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서름</t>
+        </is>
+      </c>
       <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
@@ -3016,19 +2988,20 @@
         <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F65" s="2">
         <v>2</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -3051,25 +3024,24 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F66" s="2">
         <v>2</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">내</t>
         </is>
       </c>
       <c r="J66" s="4"/>
@@ -3091,24 +3063,25 @@
         <v>6</v>
       </c>
       <c r="E67" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F67" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋姑</t>
+          <t xml:space="preserve">–|潢^</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋姑</t>
+          <t xml:space="preserve">–
+潢^</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">못봤</t>
+          <t xml:space="preserve">가</t>
         </is>
       </c>
       <c r="J67" s="4"/>
@@ -3130,22 +3103,27 @@
         <v>6</v>
       </c>
       <c r="E68" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F68" s="2">
         <v>3</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㴌|姑</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I68" s="2"/>
+          <t xml:space="preserve">㴌
+姑</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">못봤</t>
+        </is>
+      </c>
       <c r="J68" s="4"/>
       <c r="K68" s="2"/>
     </row>
@@ -3165,26 +3143,22 @@
         <v>6</v>
       </c>
       <c r="E69" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F69" s="2">
         <v>3</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I69" s="2"/>
       <c r="J69" s="4"/>
       <c r="K69" s="2"/>
     </row>
@@ -3204,10 +3178,10 @@
         <v>6</v>
       </c>
       <c r="E70" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F70" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -3221,7 +3195,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">니</t>
+          <t xml:space="preserve">으</t>
         </is>
       </c>
       <c r="J70" s="4"/>
@@ -3243,22 +3217,26 @@
         <v>6</v>
       </c>
       <c r="E71" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F71" s="2">
         <v>4</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I71" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
       <c r="J71" s="4"/>
       <c r="K71" s="2"/>
     </row>
@@ -3278,20 +3256,19 @@
         <v>6</v>
       </c>
       <c r="E72" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F72" s="2">
         <v>4</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3308,33 +3285,29 @@
         </is>
       </c>
       <c r="C73" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D73" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F73" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南|潢</t>
+          <t xml:space="preserve">·|△</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南
-潢</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·
+△</t>
+        </is>
+      </c>
+      <c r="I73" s="2"/>
       <c r="J73" s="4"/>
       <c r="K73" s="2"/>
     </row>
@@ -3354,27 +3327,32 @@
         <v>7</v>
       </c>
       <c r="E74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="2">
         <v>1</v>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모</t>
-        </is>
-      </c>
-      <c r="J74" s="4"/>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南㴌|潢</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南㴌
+潢</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부모</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위 두 글자 작게 나란히: 南+氵姑?</t>
+        </is>
+      </c>
       <c r="K74" s="2"/>
     </row>
     <row r="75">
@@ -3393,19 +3371,19 @@
         <v>7</v>
       </c>
       <c r="E75" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75" s="2">
         <v>1</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I75" s="2"/>
@@ -3428,27 +3406,28 @@
         <v>7</v>
       </c>
       <c r="E76" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F76" s="2">
-        <v>2</v>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉양</t>
-        </is>
-      </c>
-      <c r="J76" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 오른쪽에 긴 사선 표시</t>
+        </is>
+      </c>
       <c r="K76" s="2"/>
     </row>
     <row r="77">
@@ -3467,22 +3446,27 @@
         <v>7</v>
       </c>
       <c r="E77" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F77" s="2">
         <v>2</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I77" s="2"/>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉양</t>
+        </is>
+      </c>
       <c r="J77" s="4"/>
       <c r="K77" s="2"/>
     </row>
@@ -3502,31 +3486,23 @@
         <v>7</v>
       </c>
       <c r="E78" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F78" s="2">
         <v>2</v>
       </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서/설?</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I78" s="2"/>
+      <c r="J78" s="4"/>
       <c r="K78" s="2"/>
     </row>
     <row r="79">
@@ -3545,26 +3521,22 @@
         <v>7</v>
       </c>
       <c r="E79" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F79" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">글</t>
-        </is>
-      </c>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I79" s="2"/>
       <c r="J79" s="4"/>
       <c r="K79" s="2"/>
     </row>
@@ -3584,22 +3556,27 @@
         <v>7</v>
       </c>
       <c r="E80" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80" s="2">
         <v>3</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">南|潢^</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I80" s="2"/>
+          <t xml:space="preserve">南
+潢^</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">글</t>
+        </is>
+      </c>
       <c r="J80" s="4"/>
       <c r="K80" s="2"/>
     </row>
@@ -3619,20 +3596,19 @@
         <v>7</v>
       </c>
       <c r="E81" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F81" s="2">
         <v>3</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|△</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-△</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I81" s="2"/>
@@ -3655,26 +3631,23 @@
         <v>7</v>
       </c>
       <c r="E82" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F82" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">·|△</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·
+△</t>
+        </is>
+      </c>
+      <c r="I82" s="2"/>
       <c r="J82" s="4"/>
       <c r="K82" s="2"/>
     </row>
@@ -3694,24 +3667,24 @@
         <v>7</v>
       </c>
       <c r="E83" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F83" s="2">
         <v>4</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">부</t>
+          <t xml:space="preserve">공</t>
         </is>
       </c>
       <c r="J83" s="4"/>
@@ -3733,22 +3706,26 @@
         <v>7</v>
       </c>
       <c r="E84" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F84" s="2">
         <v>4</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I84" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부</t>
+        </is>
+      </c>
       <c r="J84" s="4"/>
       <c r="K84" s="2"/>
     </row>
@@ -3762,30 +3739,30 @@
         </is>
       </c>
       <c r="C85" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E85" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F85" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">겨를</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J85" s="4"/>
@@ -3807,22 +3784,27 @@
         <v>8</v>
       </c>
       <c r="E86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" s="2">
         <v>1</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I86" s="2"/>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">겨를</t>
+        </is>
+      </c>
       <c r="J86" s="4"/>
       <c r="K86" s="2"/>
     </row>
@@ -3842,26 +3824,22 @@
         <v>8</v>
       </c>
       <c r="E87" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F87" s="2">
         <v>1</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I87" s="2"/>
       <c r="J87" s="4"/>
       <c r="K87" s="2"/>
     </row>
@@ -3881,24 +3859,24 @@
         <v>8</v>
       </c>
       <c r="E88" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F88" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">없</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J88" s="4"/>
@@ -3920,24 +3898,24 @@
         <v>8</v>
       </c>
       <c r="E89" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F89" s="2">
         <v>2</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">어</t>
+          <t xml:space="preserve">없</t>
         </is>
       </c>
       <c r="J89" s="4"/>
@@ -3959,24 +3937,24 @@
         <v>8</v>
       </c>
       <c r="E90" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F90" s="2">
         <v>2</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서</t>
+          <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="J90" s="4"/>
@@ -3998,24 +3976,24 @@
         <v>8</v>
       </c>
       <c r="E91" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F91" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">서</t>
         </is>
       </c>
       <c r="J91" s="4"/>
@@ -4037,24 +4015,24 @@
         <v>8</v>
       </c>
       <c r="E92" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F92" s="2">
         <v>3</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">허</t>
+          <t xml:space="preserve">이러</t>
         </is>
       </c>
       <c r="J92" s="4"/>
@@ -4076,24 +4054,24 @@
         <v>8</v>
       </c>
       <c r="E93" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F93" s="2">
         <v>3</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">는</t>
+          <t xml:space="preserve">허</t>
         </is>
       </c>
       <c r="J93" s="4"/>
@@ -4115,10 +4093,10 @@
         <v>8</v>
       </c>
       <c r="E94" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F94" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -4132,7 +4110,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">는</t>
         </is>
       </c>
       <c r="J94" s="4"/>
@@ -4154,22 +4132,26 @@
         <v>8</v>
       </c>
       <c r="E95" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F95" s="2">
         <v>4</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I95" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="J95" s="4"/>
       <c r="K95" s="2"/>
     </row>
@@ -4189,27 +4171,62 @@
         <v>8</v>
       </c>
       <c r="E96" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F96" s="2">
         <v>4</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I96" s="2"/>
       <c r="J96" s="4"/>
       <c r="K96" s="2"/>
     </row>
+    <row r="97">
+      <c r="A97" s="2">
+        <v>1</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/쑥대머리.png</t>
+        </is>
+      </c>
+      <c r="C97" s="2">
+        <v>8</v>
+      </c>
+      <c r="D97" s="2">
+        <v>8</v>
+      </c>
+      <c r="E97" s="2">
+        <v>12</v>
+      </c>
+      <c r="F97" s="2">
+        <v>4</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I97" s="2"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K96"/>
+  <autoFilter ref="A1:K97"/>
 </worksheet>
 </file>
 
@@ -4238,7 +4255,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="55.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4261,28 +4278,30 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="55.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">겨
 를</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南南
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南㴌
 潢</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부</t>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부
+모</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -4290,27 +4309,28 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="K3" s="29" t="inlineStr">
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">보
 고</t>
@@ -4321,7 +4341,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="29" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
@@ -4331,66 +4351,63 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="29" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="P3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋潢</t>
-        </is>
-      </c>
-      <c r="Q3" s="30" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쑥</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="55.96" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모</t>
-        </is>
-      </c>
+      <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I4" s="31" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지
 고</t>
@@ -4401,48 +4418,50 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M4" s="31"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="31"/>
+      <c r="O4" s="25"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q4" s="31" t="inlineStr">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="55.19" customHeight="1">
+    <row r="5" ht="55.96" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C5" s="32" t="inlineStr">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E5" s="32"/>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="E5" s="27"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢</t>
-        </is>
-      </c>
-      <c r="G5" s="32" t="inlineStr">
+          <t xml:space="preserve">㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서
 름</t>
@@ -4450,75 +4469,78 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="32" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="K5" s="32" t="inlineStr">
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">보
 고</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M5" s="33" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O5" s="33" t="inlineStr">
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
       </c>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
-        </is>
-      </c>
-      <c r="Q5" s="32" t="inlineStr">
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="Q5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">머
 리</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="55.19" customHeight="1">
+    <row r="6" ht="55.96" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="C6" s="29" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">없</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="E6" s="29" t="inlineStr">
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">봉
 양</t>
@@ -4526,22 +4548,24 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G6" s="29"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="29"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="K6" s="29" t="inlineStr">
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">지
 고</t>
@@ -4549,10 +4573,11 @@
       </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南</t>
-        </is>
-      </c>
-      <c r="M6" s="29" t="inlineStr">
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 는</t>
@@ -4560,10 +4585,10 @@
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="O6" s="29" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
@@ -4573,60 +4598,64 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q6" s="29"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
+      <c r="Q6" s="22"/>
+    </row>
+    <row r="7" ht="55.96" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E7" s="31"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E7" s="25"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내</t>
+        </is>
+      </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="31"/>
+      <c r="I7" s="25"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K7" s="31"/>
+      <c r="K7" s="25"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="31" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="inlineStr">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">방</t>
         </is>
@@ -4636,74 +4665,66 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q7" s="31"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
+      <c r="Q7" s="25"/>
+    </row>
+    <row r="8" ht="55.96" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="E8" s="26"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
+潢^</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전</t>
-        </is>
-      </c>
+      <c r="I8" s="26"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K8" s="32"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="K8" s="26"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="M8" s="32" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O8" s="32" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="O8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4713,36 +4734,39 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q8" s="32"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
+      <c r="Q8" s="26"/>
+    </row>
+    <row r="9" ht="55.96" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+러</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
+          <t xml:space="preserve">南
+潢^</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">글</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋姑</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr">
+          <t xml:space="preserve">㴌
+姑</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 봤</t>
@@ -4750,16 +4774,21 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I9" s="29"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전</t>
+        </is>
+      </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="K9" s="29" t="inlineStr">
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">한
 양</t>
@@ -4767,75 +4796,76 @@
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M9" s="29" t="inlineStr">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="29" t="inlineStr">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">찬</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q9" s="30" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="55.19" customHeight="1">
+    <row r="10" ht="55.96" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="E10" s="31"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I10" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뻘</t>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">별</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="K10" s="31" t="inlineStr">
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">낭
 군</t>
@@ -4846,7 +4876,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M10" s="31" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">뿐</t>
         </is>
@@ -4856,7 +4886,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O10" s="31" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -4866,20 +4896,20 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q10" s="31" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="55.19" customHeight="1">
+    <row r="11" ht="55.96" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4890,33 +4920,33 @@
 △</t>
         </is>
       </c>
-      <c r="E11" s="32"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I11" s="32" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="K11" s="32" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -4926,7 +4956,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M11" s="32" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4936,7 +4966,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O11" s="32" t="inlineStr">
+      <c r="O11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4946,30 +4976,30 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q11" s="32" t="inlineStr">
+      <c r="Q11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">형</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="55.19" customHeight="1">
+    <row r="12" ht="55.96" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="inlineStr">
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">공</t>
         </is>
@@ -4979,27 +5009,28 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="29" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="K12" s="29" t="inlineStr">
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">보
 고</t>
@@ -5010,7 +5041,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M12" s="29" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -5020,7 +5051,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="29" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5030,26 +5061,26 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="29" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">용</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="55.19" customHeight="1">
+    <row r="13" ht="55.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="31"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="E13" s="31" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -5059,89 +5090,105 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q13" s="25"/>
+    </row>
+    <row r="14" ht="55.96" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M13" s="31"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O13" s="31"/>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q13" s="31"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="32"/>
+      <c r="I14" s="26"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K14" s="32"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M14" s="32"/>
+      <c r="M14" s="26"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O14" s="32"/>
+      <c r="O14" s="26"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q14" s="32"/>
+      <c r="Q14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
@@ -589,10 +589,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
@@ -535,17 +535,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -662,7 +662,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -716,6 +716,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4100,588 +4140,588 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:Q14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B3" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="21"/>
+      <c r="D4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="21"/>
+      <c r="F4" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="7" t="s">
+      <c r="M4" s="21"/>
+      <c r="N4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="7" t="s">
+      <c r="O4" s="21"/>
+      <c r="P4" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B5" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="O5" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="Q5" s="22" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B6" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7" t="s">
+      <c r="G6" s="18"/>
+      <c r="H6" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="18"/>
+      <c r="J6" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="Q6" s="8"/>
-    </row>
-    <row r="7" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="Q6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B7" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="21"/>
+      <c r="F7" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7" t="s">
+      <c r="I7" s="21"/>
+      <c r="J7" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="7" t="s">
+      <c r="K7" s="21"/>
+      <c r="L7" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="Q7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="Q7" s="21"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B8" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="22"/>
+      <c r="F8" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="22"/>
+      <c r="J8" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="22"/>
+      <c r="L8" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="N8" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="O8" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="Q8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="Q8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B9" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="18" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B10" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="21"/>
+      <c r="F10" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="21"/>
+      <c r="H10" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B11" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="22"/>
+      <c r="F11" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="O11" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="P11" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="Q11" s="12" t="s">
+      <c r="Q11" s="22" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B12" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="P12" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="18" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B13" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="21"/>
+      <c r="D13" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="21"/>
+      <c r="H13" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="21"/>
+      <c r="J13" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="7" t="s">
+      <c r="M13" s="21"/>
+      <c r="N13" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="7" t="s">
+      <c r="O13" s="21"/>
+      <c r="P13" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="Q13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="Q13" s="21"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B14" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="22"/>
+      <c r="D14" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="22"/>
+      <c r="H14" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="22"/>
+      <c r="J14" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="7" t="s">
+      <c r="M14" s="22"/>
+      <c r="N14" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="O14" s="12"/>
-      <c r="P14" s="7" t="s">
+      <c r="O14" s="22"/>
+      <c r="P14" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="Q14" s="12"/>
+      <c r="Q14" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4689,7 +4729,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="76" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
+++ b/sheets/민요/검수/쑥대머리 (단가 중모리).xlsx
@@ -4146,26 +4146,26 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="15" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.52" customHeight="true">
       <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4185,7 +4185,7 @@
       <c r="P2" s="16"/>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B3" s="17" t="s">
         <v>51</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B4" s="17" t="s">
         <v>60</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B5" s="17" t="s">
         <v>98</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B6" s="17" t="s">
         <v>46</v>
       </c>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Q6" s="18"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B7" s="17" t="s">
         <v>48</v>
       </c>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="Q7" s="21"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B8" s="17" t="s">
         <v>55</v>
       </c>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="Q8" s="22"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B9" s="17" t="s">
         <v>98</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B10" s="17" t="s">
         <v>55</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B11" s="17" t="s">
         <v>57</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B12" s="17" t="s">
         <v>57</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B13" s="17" t="s">
         <v>60</v>
       </c>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="Q13" s="21"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B14" s="17" t="s">
         <v>139</v>
       </c>
@@ -4729,7 +4729,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
